--- a/docs/reports/连通标注_2026-07-04_分表/8_关键频道.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/8_关键频道.xlsx
@@ -1461,12 +1461,12 @@
       </c>
       <c r="K3" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K4" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="K5" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="K6" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="K7" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="K8" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="K9" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="K10" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K11" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K12" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K13" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="K14" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="K15" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="K16" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="K17" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K18" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K19" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="K20" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="K21" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="K22" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="K23" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="K24" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="K25" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K26" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="K27" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="K28" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="K29" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="K30" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="K31" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="K32" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="K33" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="K34" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="K35" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="K36" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="K37" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="K38" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="K39" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="K40" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="K41" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="K42" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="K43" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="K44" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="K45" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="K46" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="K47" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="K48" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="K49" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="K50" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="K51" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="K52" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="K53" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="K54" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="K55" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="K56" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="K57" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="K58" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="K59" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="K60" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="K61" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="K62" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="K63" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="K64" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="K65" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="K66" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="K67" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="K68" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="K69" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="K70" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="K71" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K72" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="K73" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K74" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="K75" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="K76" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="K77" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="K78" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="K79" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="K80" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="K81" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="K82" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="K83" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="K84" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K85" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="K86" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="K87" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K88" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="K89" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="K90" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="K91" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="K92" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="K93" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="K94" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="K95" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6857,12 +6857,12 @@
       </c>
       <c r="K96" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="K97" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="K98" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="K99" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="K100" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="K101" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="K102" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="K103" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="K104" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="K105" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="K106" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="K107" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="K108" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="K109" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="K110" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="K111" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="K112" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="K113" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="K114" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="K115" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="K116" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="K117" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="K118" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="K119" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="K120" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="K121" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="K122" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="K123" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="K124" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="K125" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="K126" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="K127" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -8716,12 +8716,12 @@
       </c>
       <c r="K128" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K129" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="K130" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="K131" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="K132" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="K133" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K134" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="K135" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="K136" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="K137" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="K138" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K139" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="K140" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K141" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="K142" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="K143" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="K144" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K145" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="K146" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="K147" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="K148" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="K149" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -9994,12 +9994,12 @@
       </c>
       <c r="K150" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="K151" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10112,12 +10112,12 @@
       </c>
       <c r="K152" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="K153" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10230,12 +10230,12 @@
       </c>
       <c r="K154" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="K155" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10348,12 +10348,12 @@
       </c>
       <c r="K156" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10407,12 +10407,12 @@
       </c>
       <c r="K157" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="K158" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="K159" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10584,12 +10584,12 @@
       </c>
       <c r="K160" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="K161" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="K162" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10761,12 +10761,12 @@
       </c>
       <c r="K163" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10820,12 +10820,12 @@
       </c>
       <c r="K164" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10879,12 +10879,12 @@
       </c>
       <c r="K165" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10938,12 +10938,12 @@
       </c>
       <c r="K166" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="K167" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11056,12 +11056,12 @@
       </c>
       <c r="K168" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11115,12 +11115,12 @@
       </c>
       <c r="K169" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="K170" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11233,12 +11233,12 @@
       </c>
       <c r="K171" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11292,12 +11292,12 @@
       </c>
       <c r="K172" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11351,12 +11351,12 @@
       </c>
       <c r="K173" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="K174" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="K175" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="K176" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11585,12 +11585,12 @@
       </c>
       <c r="K177" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11643,12 +11643,12 @@
       </c>
       <c r="K178" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="K179" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="K180" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="K181" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="K182" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="K183" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -11994,12 +11994,12 @@
       </c>
       <c r="K184" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -12053,12 +12053,12 @@
       </c>
       <c r="K185" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="K186" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="K187" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -12229,12 +12229,12 @@
       </c>
       <c r="K188" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -12288,12 +12288,12 @@
       </c>
       <c r="K189" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>URL 含非法字符(注册表数据问题)</t>
+          <t>URL 含非法字符</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="K190" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="K191" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="K192" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="K193" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="K194" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="K195" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="K196" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="K197" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="K198" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="K199" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="K200" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="K201" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="K202" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13100,12 +13100,12 @@
       </c>
       <c r="K203" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="K204" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="K205" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="K206" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="K207" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="K208" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="K209" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="K210" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="K211" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K212" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="K213" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="K214" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="K215" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="K216" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -13912,12 +13912,12 @@
       </c>
       <c r="K217" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="K218" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="K219" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="K220" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="K221" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="K222" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="K223" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="K224" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="K225" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="K226" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="K227" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="K228" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="K229" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="K230" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="K231" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K232" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="K233" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="K234" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="K235" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="K236" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="K237" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15082,12 +15082,12 @@
       </c>
       <c r="K238" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15132,12 +15132,12 @@
       </c>
       <c r="K239" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="K240" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="K241" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15290,12 +15290,12 @@
       </c>
       <c r="K242" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15340,12 +15340,12 @@
       </c>
       <c r="K243" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="K244" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -15448,12 +15448,12 @@
       </c>
       <c r="K245" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -15498,12 +15498,12 @@
       </c>
       <c r="K246" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="K247" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="K248" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -15656,12 +15656,12 @@
       </c>
       <c r="K249" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15710,7 @@
       </c>
       <c r="K250" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="K251" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="K252" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="K253" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15922,12 +15922,12 @@
       </c>
       <c r="K254" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="K255" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="K256" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="K257" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -16134,12 +16134,12 @@
       </c>
       <c r="K258" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="K259" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -16238,12 +16238,12 @@
       </c>
       <c r="K260" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16288,12 +16288,12 @@
       </c>
       <c r="K261" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16338,12 +16338,12 @@
       </c>
       <c r="K262" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16388,12 +16388,12 @@
       </c>
       <c r="K263" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16438,12 +16438,12 @@
       </c>
       <c r="K264" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16488,12 +16488,12 @@
       </c>
       <c r="K265" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16538,12 +16538,12 @@
       </c>
       <c r="K266" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16588,12 +16588,12 @@
       </c>
       <c r="K267" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16638,12 +16638,12 @@
       </c>
       <c r="K268" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="K269" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -16742,12 +16742,12 @@
       </c>
       <c r="K270" s="185" t="inlineStr">
         <is>
-          <t>📧 需邮箱网关</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>邮件订阅类,需 IMAP/webhook 集成</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16800,12 +16800,12 @@
       </c>
       <c r="K271" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16858,12 +16858,12 @@
       </c>
       <c r="K272" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16916,12 +16916,12 @@
       </c>
       <c r="K273" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -16974,12 +16974,12 @@
       </c>
       <c r="K274" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17032,12 +17032,12 @@
       </c>
       <c r="K275" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17090,12 +17090,12 @@
       </c>
       <c r="K276" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17148,12 +17148,12 @@
       </c>
       <c r="K277" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
       </c>
       <c r="K278" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="K279" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17322,12 +17322,12 @@
       </c>
       <c r="K280" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17380,12 +17380,12 @@
       </c>
       <c r="K281" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17438,12 +17438,12 @@
       </c>
       <c r="K282" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17496,12 +17496,12 @@
       </c>
       <c r="K283" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17554,12 +17554,12 @@
       </c>
       <c r="K284" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17612,12 +17612,12 @@
       </c>
       <c r="K285" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17670,12 +17670,12 @@
       </c>
       <c r="K286" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17728,12 +17728,12 @@
       </c>
       <c r="K287" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17786,12 +17786,12 @@
       </c>
       <c r="K288" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17844,12 +17844,12 @@
       </c>
       <c r="K289" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="K290" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -17960,12 +17960,12 @@
       </c>
       <c r="K291" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18018,12 +18018,12 @@
       </c>
       <c r="K292" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18076,12 +18076,12 @@
       </c>
       <c r="K293" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18134,12 +18134,12 @@
       </c>
       <c r="K294" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="K295" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18250,12 +18250,12 @@
       </c>
       <c r="K296" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18308,12 +18308,12 @@
       </c>
       <c r="K297" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18366,12 +18366,12 @@
       </c>
       <c r="K298" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18424,12 +18424,12 @@
       </c>
       <c r="K299" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18482,12 +18482,12 @@
       </c>
       <c r="K300" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18540,12 +18540,12 @@
       </c>
       <c r="K301" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18598,12 +18598,12 @@
       </c>
       <c r="K302" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18656,12 +18656,12 @@
       </c>
       <c r="K303" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18714,12 +18714,12 @@
       </c>
       <c r="K304" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18772,12 +18772,12 @@
       </c>
       <c r="K305" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18830,12 +18830,12 @@
       </c>
       <c r="K306" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18888,12 +18888,12 @@
       </c>
       <c r="K307" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -18946,12 +18946,12 @@
       </c>
       <c r="K308" s="185" t="inlineStr">
         <is>
-          <t>➖ 无URL</t>
+          <t>➖ 无链接未验证</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>注册表行内无可抓取链接</t>
+          <t>注册表行内无可验证链接</t>
         </is>
       </c>
     </row>
@@ -19004,12 +19004,12 @@
       </c>
       <c r="K309" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19062,12 +19062,12 @@
       </c>
       <c r="K310" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19120,12 +19120,12 @@
       </c>
       <c r="K311" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19178,12 +19178,12 @@
       </c>
       <c r="K312" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19247,12 +19247,12 @@
       </c>
       <c r="K314" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19305,12 +19305,12 @@
       </c>
       <c r="K315" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19363,12 +19363,12 @@
       </c>
       <c r="K316" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19421,12 +19421,12 @@
       </c>
       <c r="K317" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19479,12 +19479,12 @@
       </c>
       <c r="K318" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19537,12 +19537,12 @@
       </c>
       <c r="K319" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
